--- a/cucumber-for-appian/src/test/resources/testdata/End2End/05_NovatedApp_End2End.xlsx
+++ b/cucumber-for-appian/src/test/resources/testdata/End2End/05_NovatedApp_End2End.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="87">
   <si>
     <t>TC ID</t>
   </si>
@@ -158,19 +158,22 @@
     <t>Fuel Card</t>
   </si>
   <si>
+    <t>8956</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
     <t>Lost</t>
   </si>
   <si>
-    <t>REQ-687</t>
+    <t>REQ-166</t>
   </si>
   <si>
     <t>ORIX Motorpass</t>
   </si>
   <si>
-    <t>13 May 2026 01:44 PM</t>
+    <t>30 Jul 2026 05:27 PM</t>
   </si>
   <si>
     <t>Replacement</t>
@@ -179,25 +182,28 @@
     <t>Mr</t>
   </si>
   <si>
-    <t>David</t>
-  </si>
-  <si>
-    <t>Stewart</t>
-  </si>
-  <si>
-    <t>30/10/1997</t>
-  </si>
-  <si>
-    <t>0499999999</t>
-  </si>
-  <si>
-    <t>visionpro101@gmail.com.test</t>
+    <t>Sudeep</t>
+  </si>
+  <si>
+    <t>Shakya</t>
+  </si>
+  <si>
+    <t>27 Jun 1986</t>
+  </si>
+  <si>
+    <t>333665987</t>
+  </si>
+  <si>
+    <t>sudeep.shakya@outlook.com.test</t>
   </si>
   <si>
     <t>Your Residential Address *</t>
   </si>
   <si>
-    <t>-</t>
+    <t>QBE Management Services Pty Ltd</t>
+  </si>
+  <si>
+    <t>25 Sept 2026</t>
   </si>
   <si>
     <t>TC002</t>
@@ -278,52 +284,10 @@
     <t>No Number Info</t>
   </si>
   <si>
-    <t>CPK418</t>
-  </si>
-  <si>
-    <t>VOLVO C40</t>
-  </si>
-  <si>
-    <t>25 Sept 2026</t>
-  </si>
-  <si>
-    <t>REQ-689</t>
-  </si>
-  <si>
-    <t>13 May 2026 02:11 PM</t>
-  </si>
-  <si>
-    <t>5220</t>
-  </si>
-  <si>
-    <t>YKQ26Y</t>
-  </si>
-  <si>
-    <t>MAZDA CX-5</t>
-  </si>
-  <si>
-    <t>53100</t>
-  </si>
-  <si>
-    <t>Neil</t>
-  </si>
-  <si>
-    <t>Jones</t>
-  </si>
-  <si>
-    <t>01/06/2000</t>
-  </si>
-  <si>
-    <t>0400123146</t>
-  </si>
-  <si>
-    <t>neil.jones@exxonmobil.com.test</t>
-  </si>
-  <si>
-    <t>Guild Insurance Ltd</t>
-  </si>
-  <si>
-    <t>REQ-737</t>
+    <t>Notifications (0)</t>
+  </si>
+  <si>
+    <t>There are no Current quotes to display</t>
   </si>
 </sst>
 </file>
@@ -1488,7 +1452,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="55.2" spans="1:41">
+    <row r="2" s="2" customFormat="1" ht="96.6" spans="1:41">
       <c r="A2" s="4" t="s">
         <v>41</v>
       </c>
@@ -1496,7 +1460,7 @@
         <v>42</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>91</v>
+        <v>43</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -1504,215 +1468,215 @@
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="S2" s="4"/>
       <c r="T2" s="4"/>
       <c r="U2" s="4" t="s">
-        <v>98</v>
+        <v>46</v>
       </c>
       <c r="V2" s="7" t="str">
         <f>TEXT(E2,"#,##0")&amp;" km"</f>
         <v>0 km</v>
       </c>
       <c r="W2" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="X2" s="7"/>
       <c r="Y2" s="7" t="s">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="Z2" s="7" t="s">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="AA2" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AB2" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AC2" s="7" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="AD2" s="7" t="s">
-        <v>93</v>
+        <v>52</v>
       </c>
       <c r="AE2" s="7" t="str">
         <f>_xlfn.CONCAT(AC2," ",AD2)</f>
-        <v>Neil Jones</v>
+        <v>Sudeep Shakya</v>
       </c>
       <c r="AF2" s="7" t="s">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="AG2" s="7" t="s">
-        <v>95</v>
+        <v>54</v>
       </c>
       <c r="AH2" s="7" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="AI2" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AJ2" s="7" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="AK2" s="7" t="str">
         <f>AM2&amp;" - "&amp;AL2</f>
-        <v>MAZDA CX-5 - YKQ26Y</v>
+        <v>There are no Current quotes to display - Notifications (0)</v>
       </c>
       <c r="AL2" s="7" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="AM2" s="7" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="AN2" s="7" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="AO2" s="7"/>
     </row>
     <row r="3" s="2" customFormat="1" ht="82.8" spans="1:41">
       <c r="A3" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="S3" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="U3" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="V3" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="W3" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="X3" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Y3" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="Z3" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AA3" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="AB3" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AC3" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="AD3" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="AE3" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AF3" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="AG3" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH3" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI3" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AJ3" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AK3" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AL3" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AM3" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AN3" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AO3" s="4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:41">

--- a/cucumber-for-appian/src/test/resources/testdata/End2End/05_NovatedApp_End2End.xlsx
+++ b/cucumber-for-appian/src/test/resources/testdata/End2End/05_NovatedApp_End2End.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="106">
   <si>
     <t>TC ID</t>
   </si>
@@ -324,6 +324,39 @@
   <si>
     <t>Latest Reading (kms)
 86,521 km</t>
+  </si>
+  <si>
+    <t>Latest Reading (kms)
+89,062 km</t>
+  </si>
+  <si>
+    <t>Latest Reading (kms)
+89,166 km</t>
+  </si>
+  <si>
+    <t>Latest Reading (kms)
+21,028 km</t>
+  </si>
+  <si>
+    <t>Mr</t>
+  </si>
+  <si>
+    <t>ALFVU</t>
+  </si>
+  <si>
+    <t>ZZNXTGSP</t>
+  </si>
+  <si>
+    <t>0455 512 334</t>
+  </si>
+  <si>
+    <t>139638@omsrefresh.com</t>
+  </si>
+  <si>
+    <t>BHP Iron Ore Pty Ltd</t>
+  </si>
+  <si>
+    <t>83 Fulham Rd ALPHINGTON VIC 3078</t>
   </si>
 </sst>
 </file>
@@ -873,7 +906,7 @@
         <v>40</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
@@ -923,7 +956,7 @@
         <v>44</v>
       </c>
       <c r="X2" s="6" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="Y2" s="6" t="s">
         <v>45</v>
@@ -935,32 +968,32 @@
         <v>46</v>
       </c>
       <c r="AB2" s="6" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="AC2" s="6" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AD2" s="6" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="AE2" s="6" t="str">
         <f>_xlfn.CONCAT(AC2," ",AD2)</f>
-        <v>SXBHG WHKDOPZ</v>
+        <v>ALFVU ZZNXTGSP</v>
       </c>
       <c r="AF2" s="6" t="s">
         <v>48</v>
       </c>
       <c r="AG2" s="6" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="AH2" s="6" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="AI2" s="6" t="s">
         <v>51</v>
       </c>
       <c r="AJ2" s="6" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="AK2" s="6" t="str">
         <f>AM2&amp;" - "&amp;AL2</f>
